--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/22,10,26 ПОКОМ ЗПФ/дв 22,10,26 днрсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/22,10,26 ПОКОМ ЗПФ/дв 22,10,26 днрсч пок зпф.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\10,26\22,10,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F0AC82-9885-4D3C-8E26-B247C4D1A51F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC27003-DD75-4496-98EA-CD2D0B5B9FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AO$88</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -631,10 +623,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="167" formatCode="0.0_ ;[Red]\-0.0\ "/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -764,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -785,16 +778,13 @@
     <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1098,6 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AX497"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1114,10 +1105,10 @@
     <col min="13" max="14" width="0.28515625" customWidth="1"/>
     <col min="15" max="17" width="6" customWidth="1"/>
     <col min="18" max="20" width="7" customWidth="1"/>
-    <col min="21" max="21" width="7" style="25" customWidth="1"/>
+    <col min="21" max="21" width="7" style="24" customWidth="1"/>
     <col min="22" max="23" width="5" customWidth="1"/>
     <col min="24" max="33" width="6" customWidth="1"/>
-    <col min="34" max="34" width="33.28515625" customWidth="1"/>
+    <col min="34" max="34" width="23.140625" customWidth="1"/>
     <col min="35" max="35" width="6.5703125" customWidth="1"/>
     <col min="36" max="36" width="6" style="6" customWidth="1"/>
     <col min="37" max="37" width="7" style="12" customWidth="1"/>
@@ -1146,7 +1137,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="29">
+      <c r="S1" s="25">
         <v>3.6</v>
       </c>
       <c r="T1" s="1"/>
@@ -1372,7 +1363,7 @@
       <c r="AW3" s="1"/>
       <c r="AX3" s="1"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1454,7 +1445,7 @@
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1633,7 +1624,7 @@
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
       <c r="T6" s="16"/>
-      <c r="U6" s="26"/>
+      <c r="U6" s="14"/>
       <c r="V6" s="14">
         <f t="shared" ref="V6:V37" si="4">(F6+O6+P6+T6)/Q6</f>
         <v>7.8518518518518521</v>
@@ -1690,7 +1681,7 @@
       <c r="AW6" s="1"/>
       <c r="AX6" s="1"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>46</v>
       </c>
@@ -1737,7 +1728,7 @@
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
-      <c r="U7" s="26"/>
+      <c r="U7" s="14"/>
       <c r="V7" s="14">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -1794,8 +1785,8 @@
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1836,7 +1827,7 @@
         <f>AJ8*AK8</f>
         <v>0</v>
       </c>
-      <c r="U8" s="27"/>
+      <c r="U8" s="1"/>
       <c r="V8" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -1913,7 +1904,7 @@
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>51</v>
       </c>
@@ -1962,7 +1953,7 @@
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
-      <c r="U9" s="26"/>
+      <c r="U9" s="14"/>
       <c r="V9" s="14">
         <f t="shared" si="4"/>
         <v>19.733178654292342</v>
@@ -2073,7 +2064,7 @@
         <f>AJ10*AK10</f>
         <v>0</v>
       </c>
-      <c r="U10" s="27"/>
+      <c r="U10" s="1"/>
       <c r="V10" s="1">
         <f t="shared" si="4"/>
         <v>30.393939393939394</v>
@@ -2197,7 +2188,7 @@
       <c r="R11" s="16"/>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
-      <c r="U11" s="26"/>
+      <c r="U11" s="14"/>
       <c r="V11" s="14">
         <f t="shared" si="4"/>
         <v>17.956989247311828</v>
@@ -2254,7 +2245,7 @@
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -2303,7 +2294,7 @@
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
-      <c r="U12" s="26"/>
+      <c r="U12" s="14"/>
       <c r="V12" s="14">
         <f t="shared" si="4"/>
         <v>6.25</v>
@@ -2360,7 +2351,7 @@
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>60</v>
       </c>
@@ -2409,7 +2400,7 @@
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
       <c r="T13" s="16"/>
-      <c r="U13" s="26"/>
+      <c r="U13" s="14"/>
       <c r="V13" s="14">
         <f t="shared" si="4"/>
         <v>4.6788990825688073</v>
@@ -2466,7 +2457,7 @@
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2515,7 +2506,7 @@
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
       <c r="T14" s="16"/>
-      <c r="U14" s="26"/>
+      <c r="U14" s="14"/>
       <c r="V14" s="14">
         <f t="shared" si="4"/>
         <v>6.0220125786163523</v>
@@ -2572,7 +2563,7 @@
       <c r="AW14" s="1"/>
       <c r="AX14" s="1"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
@@ -2631,7 +2622,7 @@
         <f>AJ15*AK15</f>
         <v>840</v>
       </c>
-      <c r="U15" s="27"/>
+      <c r="U15" s="1"/>
       <c r="V15" s="1">
         <f t="shared" si="4"/>
         <v>17.560975609756099</v>
@@ -2706,7 +2697,7 @@
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
@@ -2763,7 +2754,7 @@
         <f>AJ16*AK16</f>
         <v>1008</v>
       </c>
-      <c r="U16" s="27"/>
+      <c r="U16" s="1"/>
       <c r="V16" s="1">
         <f t="shared" si="4"/>
         <v>17.622673434856175</v>
@@ -2838,7 +2829,7 @@
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>68</v>
       </c>
@@ -2885,7 +2876,7 @@
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
       <c r="T17" s="16"/>
-      <c r="U17" s="26"/>
+      <c r="U17" s="14"/>
       <c r="V17" s="14">
         <f t="shared" si="4"/>
         <v>1.9799691833590136</v>
@@ -2942,7 +2933,7 @@
       <c r="AW17" s="1"/>
       <c r="AX17" s="1"/>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,7 +2992,7 @@
         <f>AJ18*AK18</f>
         <v>504</v>
       </c>
-      <c r="U18" s="27"/>
+      <c r="U18" s="1"/>
       <c r="V18" s="1">
         <f t="shared" si="4"/>
         <v>17.187088274044793</v>
@@ -3076,7 +3067,7 @@
       <c r="AW18" s="1"/>
       <c r="AX18" s="1"/>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
@@ -3131,7 +3122,7 @@
         <f>AJ19*AK19</f>
         <v>168</v>
       </c>
-      <c r="U19" s="27"/>
+      <c r="U19" s="1"/>
       <c r="V19" s="1">
         <f t="shared" si="4"/>
         <v>17.202602230483272</v>
@@ -3253,7 +3244,7 @@
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
-      <c r="U20" s="26"/>
+      <c r="U20" s="14"/>
       <c r="V20" s="14">
         <f t="shared" si="4"/>
         <v>8.9232409381663107</v>
@@ -3359,7 +3350,7 @@
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
-      <c r="U21" s="26"/>
+      <c r="U21" s="14"/>
       <c r="V21" s="14">
         <f t="shared" si="4"/>
         <v>2.9671717171717171</v>
@@ -3475,7 +3466,7 @@
         <f t="shared" ref="T22:T27" si="7">AJ22*AK22</f>
         <v>1176</v>
       </c>
-      <c r="U22" s="27"/>
+      <c r="U22" s="1"/>
       <c r="V22" s="1">
         <f t="shared" si="4"/>
         <v>18.01957831325301</v>
@@ -3607,7 +3598,7 @@
         <f t="shared" si="7"/>
         <v>784</v>
       </c>
-      <c r="U23" s="27"/>
+      <c r="U23" s="1"/>
       <c r="V23" s="1">
         <f t="shared" si="4"/>
         <v>17.108585858585858</v>
@@ -3682,7 +3673,7 @@
       <c r="AW23" s="1"/>
       <c r="AX23" s="1"/>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>78</v>
       </c>
@@ -3734,7 +3725,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U24" s="27"/>
+      <c r="U24" s="1"/>
       <c r="V24" s="1">
         <f t="shared" si="4"/>
         <v>16.906077348066297</v>
@@ -3809,7 +3800,7 @@
       <c r="AW24" s="1"/>
       <c r="AX24" s="1"/>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>80</v>
       </c>
@@ -3853,17 +3844,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R25" s="23">
+      <c r="R25" s="22">
         <v>0</v>
       </c>
-      <c r="S25" s="23">
+      <c r="S25" s="22">
         <v>0</v>
       </c>
-      <c r="T25" s="23">
+      <c r="T25" s="22">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U25" s="28"/>
+      <c r="U25" s="23"/>
       <c r="V25" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -3902,7 +3893,7 @@
       <c r="AG25" s="1">
         <v>33</v>
       </c>
-      <c r="AH25" s="24" t="s">
+      <c r="AH25" s="23" t="s">
         <v>82</v>
       </c>
       <c r="AI25" s="1">
@@ -3940,7 +3931,7 @@
       <c r="AW25" s="1"/>
       <c r="AX25" s="1"/>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>83</v>
       </c>
@@ -3997,7 +3988,7 @@
         <f t="shared" si="7"/>
         <v>336</v>
       </c>
-      <c r="U26" s="27"/>
+      <c r="U26" s="1"/>
       <c r="V26" s="1">
         <f t="shared" si="4"/>
         <v>16.373390557939913</v>
@@ -4072,7 +4063,7 @@
       <c r="AW26" s="1"/>
       <c r="AX26" s="1"/>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>85</v>
       </c>
@@ -4124,14 +4115,14 @@
         <v>117.20000000000005</v>
       </c>
       <c r="S27" s="5">
-        <f t="shared" ref="S26:S27" si="12">14*Q27-P27-O27-F27+Q27*$S$1</f>
+        <f t="shared" ref="S27" si="12">14*Q27-P27-O27-F27+Q27*$S$1</f>
         <v>530.48</v>
       </c>
       <c r="T27" s="5">
         <f t="shared" si="7"/>
         <v>504</v>
       </c>
-      <c r="U27" s="27"/>
+      <c r="U27" s="1"/>
       <c r="V27" s="1">
         <f t="shared" si="4"/>
         <v>17.369337979094077</v>
@@ -4247,7 +4238,7 @@
       <c r="R28" s="16"/>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
-      <c r="U28" s="26"/>
+      <c r="U28" s="14"/>
       <c r="V28" s="14" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -4363,7 +4354,7 @@
         <f t="shared" ref="T29:T35" si="13">AJ29*AK29</f>
         <v>672</v>
       </c>
-      <c r="U29" s="27"/>
+      <c r="U29" s="1"/>
       <c r="V29" s="1">
         <f t="shared" si="4"/>
         <v>17.907801418439718</v>
@@ -4438,7 +4429,7 @@
       <c r="AW29" s="1"/>
       <c r="AX29" s="1"/>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>89</v>
       </c>
@@ -4490,7 +4481,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U30" s="27"/>
+      <c r="U30" s="1"/>
       <c r="V30" s="1">
         <f t="shared" si="4"/>
         <v>26.020770010131713</v>
@@ -4565,7 +4556,7 @@
       <c r="AW30" s="1"/>
       <c r="AX30" s="1"/>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>92</v>
       </c>
@@ -4617,7 +4608,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U31" s="27"/>
+      <c r="U31" s="1"/>
       <c r="V31" s="1">
         <f t="shared" si="4"/>
         <v>18.051282051282051</v>
@@ -4692,7 +4683,7 @@
       <c r="AW31" s="1"/>
       <c r="AX31" s="1"/>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>94</v>
       </c>
@@ -4746,7 +4737,7 @@
         <f t="shared" si="13"/>
         <v>378</v>
       </c>
-      <c r="U32" s="27">
+      <c r="U32" s="1">
         <v>400</v>
       </c>
       <c r="V32" s="1">
@@ -4823,8 +4814,8 @@
       <c r="AW32" s="1"/>
       <c r="AX32" s="1"/>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -4865,7 +4856,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U33" s="27"/>
+      <c r="U33" s="1"/>
       <c r="V33" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -4942,7 +4933,7 @@
       <c r="AW33" s="1"/>
       <c r="AX33" s="1"/>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
@@ -5001,7 +4992,7 @@
         <f t="shared" si="13"/>
         <v>756</v>
       </c>
-      <c r="U34" s="27"/>
+      <c r="U34" s="1"/>
       <c r="V34" s="1">
         <f t="shared" si="4"/>
         <v>17.425742574257423</v>
@@ -5076,7 +5067,7 @@
       <c r="AW34" s="1"/>
       <c r="AX34" s="1"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>99</v>
       </c>
@@ -5128,7 +5119,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U35" s="27"/>
+      <c r="U35" s="1"/>
       <c r="V35" s="1">
         <f t="shared" si="4"/>
         <v>17.700296735905042</v>
@@ -5203,7 +5194,7 @@
       <c r="AW35" s="1"/>
       <c r="AX35" s="1"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>101</v>
       </c>
@@ -5252,7 +5243,7 @@
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
       <c r="T36" s="16"/>
-      <c r="U36" s="26"/>
+      <c r="U36" s="14"/>
       <c r="V36" s="14">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -5309,7 +5300,7 @@
       <c r="AW36" s="1"/>
       <c r="AX36" s="1"/>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>102</v>
       </c>
@@ -5367,7 +5358,7 @@
         <f t="shared" ref="T37:T62" si="18">AJ37*AK37</f>
         <v>432</v>
       </c>
-      <c r="U37" s="27">
+      <c r="U37" s="1">
         <v>500</v>
       </c>
       <c r="V37" s="1">
@@ -5444,7 +5435,7 @@
       <c r="AW37" s="1"/>
       <c r="AX37" s="1"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>104</v>
       </c>
@@ -5496,7 +5487,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U38" s="27"/>
+      <c r="U38" s="1"/>
       <c r="V38" s="1">
         <f t="shared" ref="V38:V69" si="25">(F38+O38+P38+T38)/Q38</f>
         <v>26.743929359823401</v>
@@ -5571,7 +5562,7 @@
       <c r="AW38" s="1"/>
       <c r="AX38" s="1"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>105</v>
       </c>
@@ -5630,7 +5621,7 @@
         <f t="shared" si="18"/>
         <v>2016</v>
       </c>
-      <c r="U39" s="27"/>
+      <c r="U39" s="1"/>
       <c r="V39" s="1">
         <f t="shared" si="25"/>
         <v>17.638081395348838</v>
@@ -5705,7 +5696,7 @@
       <c r="AW39" s="1"/>
       <c r="AX39" s="1"/>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>107</v>
       </c>
@@ -5764,7 +5755,7 @@
         <f t="shared" si="18"/>
         <v>1176</v>
       </c>
-      <c r="U40" s="27"/>
+      <c r="U40" s="1"/>
       <c r="V40" s="1">
         <f t="shared" si="25"/>
         <v>17.456140350877192</v>
@@ -5839,7 +5830,7 @@
       <c r="AW40" s="1"/>
       <c r="AX40" s="1"/>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>109</v>
       </c>
@@ -5898,7 +5889,7 @@
         <f t="shared" si="18"/>
         <v>1008</v>
       </c>
-      <c r="U41" s="27"/>
+      <c r="U41" s="1"/>
       <c r="V41" s="1">
         <f t="shared" si="25"/>
         <v>17.993150684931507</v>
@@ -5973,7 +5964,7 @@
       <c r="AW41" s="1"/>
       <c r="AX41" s="1"/>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>59</v>
       </c>
@@ -6030,7 +6021,7 @@
         <f t="shared" si="18"/>
         <v>168</v>
       </c>
-      <c r="U42" s="27"/>
+      <c r="U42" s="1"/>
       <c r="V42" s="1">
         <f t="shared" si="25"/>
         <v>18.17910447761194</v>
@@ -6105,7 +6096,7 @@
       <c r="AW42" s="1"/>
       <c r="AX42" s="1"/>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
@@ -6160,7 +6151,7 @@
         <f t="shared" si="18"/>
         <v>192</v>
       </c>
-      <c r="U43" s="27"/>
+      <c r="U43" s="1"/>
       <c r="V43" s="1">
         <f t="shared" si="25"/>
         <v>18.053691275167786</v>
@@ -6235,7 +6226,7 @@
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
@@ -6292,7 +6283,7 @@
         <f t="shared" si="18"/>
         <v>288</v>
       </c>
-      <c r="U44" s="27"/>
+      <c r="U44" s="1"/>
       <c r="V44" s="1">
         <f t="shared" si="25"/>
         <v>17.755555555555556</v>
@@ -6367,7 +6358,7 @@
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
@@ -6407,17 +6398,17 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="R45" s="23">
+      <c r="R45" s="22">
         <v>0</v>
       </c>
-      <c r="S45" s="23">
+      <c r="S45" s="22">
         <v>0</v>
       </c>
-      <c r="T45" s="23">
+      <c r="T45" s="22">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U45" s="28"/>
+      <c r="U45" s="23"/>
       <c r="V45" s="1" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
@@ -6456,7 +6447,7 @@
       <c r="AG45" s="1">
         <v>56.2</v>
       </c>
-      <c r="AH45" s="24" t="s">
+      <c r="AH45" s="23" t="s">
         <v>82</v>
       </c>
       <c r="AI45" s="1">
@@ -6494,7 +6485,7 @@
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>118</v>
       </c>
@@ -6544,7 +6535,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U46" s="27"/>
+      <c r="U46" s="1"/>
       <c r="V46" s="1">
         <f t="shared" si="25"/>
         <v>955</v>
@@ -6621,7 +6612,7 @@
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>120</v>
       </c>
@@ -6667,7 +6658,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U47" s="27"/>
+      <c r="U47" s="1"/>
       <c r="V47" s="1" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
@@ -6744,7 +6735,7 @@
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>122</v>
       </c>
@@ -6801,7 +6792,7 @@
         <f t="shared" si="18"/>
         <v>360</v>
       </c>
-      <c r="U48" s="27"/>
+      <c r="U48" s="1"/>
       <c r="V48" s="1">
         <f t="shared" si="25"/>
         <v>18.49809885931559</v>
@@ -6876,7 +6867,7 @@
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>123</v>
       </c>
@@ -6928,7 +6919,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U49" s="27"/>
+      <c r="U49" s="1"/>
       <c r="V49" s="1">
         <f t="shared" si="25"/>
         <v>22.247191011235955</v>
@@ -7003,7 +6994,7 @@
       <c r="AW49" s="1"/>
       <c r="AX49" s="1"/>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>125</v>
       </c>
@@ -7060,7 +7051,7 @@
         <f t="shared" si="18"/>
         <v>384</v>
       </c>
-      <c r="U50" s="27"/>
+      <c r="U50" s="1"/>
       <c r="V50" s="1">
         <f t="shared" si="25"/>
         <v>19.975000000000001</v>
@@ -7135,7 +7126,7 @@
       <c r="AW50" s="1"/>
       <c r="AX50" s="1"/>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>127</v>
       </c>
@@ -7192,7 +7183,7 @@
         <f t="shared" si="18"/>
         <v>720</v>
       </c>
-      <c r="U51" s="27"/>
+      <c r="U51" s="1"/>
       <c r="V51" s="1">
         <f t="shared" si="25"/>
         <v>17.084282460136674</v>
@@ -7267,7 +7258,7 @@
       <c r="AW51" s="1"/>
       <c r="AX51" s="1"/>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>129</v>
       </c>
@@ -7324,7 +7315,7 @@
         <f t="shared" si="18"/>
         <v>240</v>
       </c>
-      <c r="U52" s="27"/>
+      <c r="U52" s="1"/>
       <c r="V52" s="1">
         <f t="shared" si="25"/>
         <v>18.066884176182707</v>
@@ -7399,7 +7390,7 @@
       <c r="AW52" s="1"/>
       <c r="AX52" s="1"/>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>131</v>
       </c>
@@ -7456,7 +7447,7 @@
         <f t="shared" si="18"/>
         <v>1080</v>
       </c>
-      <c r="U53" s="27"/>
+      <c r="U53" s="1"/>
       <c r="V53" s="1">
         <f t="shared" si="25"/>
         <v>17.434782608695652</v>
@@ -7531,7 +7522,7 @@
       <c r="AW53" s="1"/>
       <c r="AX53" s="1"/>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>133</v>
       </c>
@@ -7583,7 +7574,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U54" s="27"/>
+      <c r="U54" s="1"/>
       <c r="V54" s="1">
         <f t="shared" si="25"/>
         <v>23.26923076923077</v>
@@ -7622,7 +7613,7 @@
       <c r="AG54" s="1">
         <v>70.8</v>
       </c>
-      <c r="AH54" s="21" t="s">
+      <c r="AH54" s="20" t="s">
         <v>135</v>
       </c>
       <c r="AI54" s="1">
@@ -7660,7 +7651,7 @@
       <c r="AW54" s="1"/>
       <c r="AX54" s="1"/>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>136</v>
       </c>
@@ -7719,7 +7710,7 @@
         <f t="shared" si="18"/>
         <v>720</v>
       </c>
-      <c r="U55" s="27"/>
+      <c r="U55" s="1"/>
       <c r="V55" s="1">
         <f t="shared" si="25"/>
         <v>17.70365997638725</v>
@@ -7794,7 +7785,7 @@
       <c r="AW55" s="1"/>
       <c r="AX55" s="1"/>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>138</v>
       </c>
@@ -7851,7 +7842,7 @@
         <f t="shared" si="18"/>
         <v>960</v>
       </c>
-      <c r="U56" s="27"/>
+      <c r="U56" s="1"/>
       <c r="V56" s="1">
         <f t="shared" si="25"/>
         <v>17.430703624733475</v>
@@ -7926,7 +7917,7 @@
       <c r="AW56" s="1"/>
       <c r="AX56" s="1"/>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>140</v>
       </c>
@@ -7983,7 +7974,7 @@
         <f t="shared" si="18"/>
         <v>600</v>
       </c>
-      <c r="U57" s="27"/>
+      <c r="U57" s="1"/>
       <c r="V57" s="1">
         <f t="shared" si="25"/>
         <v>17.662650602409638</v>
@@ -8058,7 +8049,7 @@
       <c r="AW57" s="1"/>
       <c r="AX57" s="1"/>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>142</v>
       </c>
@@ -8113,7 +8104,7 @@
         <f t="shared" si="18"/>
         <v>480</v>
       </c>
-      <c r="U58" s="27"/>
+      <c r="U58" s="1"/>
       <c r="V58" s="1">
         <f t="shared" si="25"/>
         <v>16.900584795321635</v>
@@ -8188,7 +8179,7 @@
       <c r="AW58" s="1"/>
       <c r="AX58" s="1"/>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>144</v>
       </c>
@@ -8247,7 +8238,7 @@
         <f t="shared" si="18"/>
         <v>660</v>
       </c>
-      <c r="U59" s="27"/>
+      <c r="U59" s="1"/>
       <c r="V59" s="1">
         <f t="shared" si="25"/>
         <v>17.485074626865671</v>
@@ -8322,7 +8313,7 @@
       <c r="AW59" s="1"/>
       <c r="AX59" s="1"/>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>146</v>
       </c>
@@ -8379,7 +8370,7 @@
         <f t="shared" si="18"/>
         <v>192</v>
       </c>
-      <c r="U60" s="27"/>
+      <c r="U60" s="1"/>
       <c r="V60" s="1">
         <f t="shared" si="25"/>
         <v>20.675675675675674</v>
@@ -8454,7 +8445,7 @@
       <c r="AW60" s="1"/>
       <c r="AX60" s="1"/>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>148</v>
       </c>
@@ -8502,7 +8493,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U61" s="27"/>
+      <c r="U61" s="1"/>
       <c r="V61" s="1" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
@@ -8579,8 +8570,8 @@
       <c r="AW61" s="1"/>
       <c r="AX61" s="1"/>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
+    <row r="62" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -8632,7 +8623,7 @@
         <f t="shared" si="18"/>
         <v>240</v>
       </c>
-      <c r="U62" s="27"/>
+      <c r="U62" s="1"/>
       <c r="V62" s="1">
         <f t="shared" si="25"/>
         <v>17.26643598615917</v>
@@ -8707,7 +8698,7 @@
       <c r="AW62" s="1"/>
       <c r="AX62" s="1"/>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>152</v>
       </c>
@@ -8756,7 +8747,7 @@
       <c r="R63" s="16"/>
       <c r="S63" s="16"/>
       <c r="T63" s="16"/>
-      <c r="U63" s="26"/>
+      <c r="U63" s="14"/>
       <c r="V63" s="14">
         <f t="shared" si="25"/>
         <v>13.114186851211073</v>
@@ -8813,7 +8804,7 @@
       <c r="AW63" s="1"/>
       <c r="AX63" s="1"/>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
         <v>153</v>
       </c>
@@ -8872,7 +8863,7 @@
         <f>AJ64*AK64</f>
         <v>259</v>
       </c>
-      <c r="U64" s="27"/>
+      <c r="U64" s="1"/>
       <c r="V64" s="1">
         <f t="shared" si="25"/>
         <v>18.397683397683398</v>
@@ -8947,7 +8938,7 @@
       <c r="AW64" s="1"/>
       <c r="AX64" s="1"/>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>155</v>
       </c>
@@ -8994,7 +8985,7 @@
       <c r="R65" s="16"/>
       <c r="S65" s="16"/>
       <c r="T65" s="16"/>
-      <c r="U65" s="26"/>
+      <c r="U65" s="14"/>
       <c r="V65" s="14">
         <f t="shared" si="25"/>
         <v>1.2653562653562653</v>
@@ -9103,7 +9094,7 @@
       <c r="R66" s="16"/>
       <c r="S66" s="16"/>
       <c r="T66" s="16"/>
-      <c r="U66" s="26"/>
+      <c r="U66" s="14"/>
       <c r="V66" s="14">
         <f t="shared" si="25"/>
         <v>-0.2</v>
@@ -9160,7 +9151,7 @@
       <c r="AW66" s="1"/>
       <c r="AX66" s="1"/>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
         <v>157</v>
       </c>
@@ -9209,7 +9200,7 @@
       <c r="R67" s="16"/>
       <c r="S67" s="16"/>
       <c r="T67" s="16"/>
-      <c r="U67" s="26"/>
+      <c r="U67" s="14"/>
       <c r="V67" s="14">
         <f t="shared" si="25"/>
         <v>6.8527918781725887</v>
@@ -9266,7 +9257,7 @@
       <c r="AW67" s="1"/>
       <c r="AX67" s="1"/>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
         <v>158</v>
       </c>
@@ -9315,7 +9306,7 @@
       <c r="R68" s="16"/>
       <c r="S68" s="16"/>
       <c r="T68" s="16"/>
-      <c r="U68" s="26"/>
+      <c r="U68" s="14"/>
       <c r="V68" s="14">
         <f t="shared" si="25"/>
         <v>11.377118644067796</v>
@@ -9372,7 +9363,7 @@
       <c r="AW68" s="1"/>
       <c r="AX68" s="1"/>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
         <v>160</v>
       </c>
@@ -9421,7 +9412,7 @@
       <c r="R69" s="16"/>
       <c r="S69" s="16"/>
       <c r="T69" s="16"/>
-      <c r="U69" s="26"/>
+      <c r="U69" s="14"/>
       <c r="V69" s="14">
         <f t="shared" si="25"/>
         <v>17.708333333333332</v>
@@ -9478,7 +9469,7 @@
       <c r="AW69" s="1"/>
       <c r="AX69" s="1"/>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
         <v>161</v>
       </c>
@@ -9525,7 +9516,7 @@
       <c r="R70" s="16"/>
       <c r="S70" s="16"/>
       <c r="T70" s="16"/>
-      <c r="U70" s="26"/>
+      <c r="U70" s="14"/>
       <c r="V70" s="14">
         <f t="shared" ref="V70:V88" si="32">(F70+O70+P70+T70)/Q70</f>
         <v>21.989247311827956</v>
@@ -9582,7 +9573,7 @@
       <c r="AW70" s="1"/>
       <c r="AX70" s="1"/>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>162</v>
       </c>
@@ -9639,7 +9630,7 @@
         <f>AJ71*AK71</f>
         <v>420</v>
       </c>
-      <c r="U71" s="27"/>
+      <c r="U71" s="1"/>
       <c r="V71" s="1">
         <f t="shared" si="32"/>
         <v>17.1875</v>
@@ -9714,7 +9705,7 @@
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>61</v>
       </c>
@@ -9773,7 +9764,7 @@
         <f>AJ72*AK72</f>
         <v>2688</v>
       </c>
-      <c r="U72" s="27"/>
+      <c r="U72" s="1"/>
       <c r="V72" s="1">
         <f t="shared" si="32"/>
         <v>17.223382045929018</v>
@@ -9848,7 +9839,7 @@
       <c r="AW72" s="1"/>
       <c r="AX72" s="1"/>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>63</v>
       </c>
@@ -9907,7 +9898,7 @@
         <f>AJ73*AK73</f>
         <v>336</v>
       </c>
-      <c r="U73" s="27"/>
+      <c r="U73" s="1"/>
       <c r="V73" s="1">
         <f t="shared" si="32"/>
         <v>16.83235867446394</v>
@@ -9982,7 +9973,7 @@
       <c r="AW73" s="1"/>
       <c r="AX73" s="1"/>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>166</v>
       </c>
@@ -10029,7 +10020,7 @@
       <c r="R74" s="16"/>
       <c r="S74" s="16"/>
       <c r="T74" s="16"/>
-      <c r="U74" s="26"/>
+      <c r="U74" s="14"/>
       <c r="V74" s="14">
         <f t="shared" si="32"/>
         <v>10.408163265306122</v>
@@ -10092,7 +10083,7 @@
       <c r="AW74" s="1"/>
       <c r="AX74" s="1"/>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>168</v>
       </c>
@@ -10144,7 +10135,7 @@
         <f>AJ75*AK75</f>
         <v>0</v>
       </c>
-      <c r="U75" s="27"/>
+      <c r="U75" s="1"/>
       <c r="V75" s="1">
         <f t="shared" si="32"/>
         <v>102.36842105263158</v>
@@ -10221,7 +10212,7 @@
       <c r="AW75" s="1"/>
       <c r="AX75" s="1"/>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
         <v>171</v>
       </c>
@@ -10266,7 +10257,7 @@
       <c r="R76" s="16"/>
       <c r="S76" s="16"/>
       <c r="T76" s="16"/>
-      <c r="U76" s="26"/>
+      <c r="U76" s="14"/>
       <c r="V76" s="14">
         <f t="shared" si="32"/>
         <v>115</v>
@@ -10305,7 +10296,7 @@
       <c r="AG76" s="14">
         <v>0.6</v>
       </c>
-      <c r="AH76" s="22" t="s">
+      <c r="AH76" s="21" t="s">
         <v>172</v>
       </c>
       <c r="AI76" s="14"/>
@@ -10331,7 +10322,7 @@
       <c r="AW76" s="1"/>
       <c r="AX76" s="1"/>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>173</v>
       </c>
@@ -10388,7 +10379,7 @@
         <f t="shared" ref="T77:T87" si="35">AJ77*AK77</f>
         <v>1008</v>
       </c>
-      <c r="U77" s="27"/>
+      <c r="U77" s="1"/>
       <c r="V77" s="1">
         <f t="shared" si="32"/>
         <v>17.712643678160919</v>
@@ -10463,7 +10454,7 @@
       <c r="AW77" s="1"/>
       <c r="AX77" s="1"/>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>175</v>
       </c>
@@ -10520,7 +10511,7 @@
         <f t="shared" si="35"/>
         <v>504</v>
       </c>
-      <c r="U78" s="27"/>
+      <c r="U78" s="1"/>
       <c r="V78" s="1">
         <f t="shared" si="32"/>
         <v>16.77927927927928</v>
@@ -10595,7 +10586,7 @@
       <c r="AW78" s="1"/>
       <c r="AX78" s="1"/>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>159</v>
       </c>
@@ -10654,7 +10645,7 @@
         <f t="shared" si="35"/>
         <v>1176</v>
       </c>
-      <c r="U79" s="27"/>
+      <c r="U79" s="1"/>
       <c r="V79" s="1">
         <f t="shared" si="32"/>
         <v>18.301282051282051</v>
@@ -10729,7 +10720,7 @@
       <c r="AW79" s="1"/>
       <c r="AX79" s="1"/>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>178</v>
       </c>
@@ -10775,14 +10766,14 @@
         <v>86.799999999999983</v>
       </c>
       <c r="S80" s="5">
-        <f t="shared" ref="S79:S81" si="41">14*Q80-P80-O80-F80+Q80*$S$1</f>
+        <f t="shared" ref="S80:S81" si="41">14*Q80-P80-O80-F80+Q80*$S$1</f>
         <v>152.32</v>
       </c>
       <c r="T80" s="5">
         <f t="shared" si="35"/>
         <v>168</v>
       </c>
-      <c r="U80" s="27"/>
+      <c r="U80" s="1"/>
       <c r="V80" s="1">
         <f t="shared" si="32"/>
         <v>18.461538461538463</v>
@@ -10857,7 +10848,7 @@
       <c r="AW80" s="1"/>
       <c r="AX80" s="1"/>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>180</v>
       </c>
@@ -10914,7 +10905,7 @@
         <f t="shared" si="35"/>
         <v>4032</v>
       </c>
-      <c r="U81" s="27"/>
+      <c r="U81" s="1"/>
       <c r="V81" s="1">
         <f t="shared" si="32"/>
         <v>17.641013384321223</v>
@@ -10989,7 +10980,7 @@
       <c r="AW81" s="1"/>
       <c r="AX81" s="1"/>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>53</v>
       </c>
@@ -11043,7 +11034,7 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="U82" s="27"/>
+      <c r="U82" s="1"/>
       <c r="V82" s="1">
         <f t="shared" si="32"/>
         <v>17.352941176470591</v>
@@ -11118,7 +11109,7 @@
       <c r="AW82" s="1"/>
       <c r="AX82" s="1"/>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>182</v>
       </c>
@@ -11175,7 +11166,7 @@
         <f t="shared" si="35"/>
         <v>420</v>
       </c>
-      <c r="U83" s="27"/>
+      <c r="U83" s="1"/>
       <c r="V83" s="1">
         <f t="shared" si="32"/>
         <v>17.535410764872523</v>
@@ -11250,7 +11241,7 @@
       <c r="AW83" s="1"/>
       <c r="AX83" s="1"/>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>184</v>
       </c>
@@ -11307,7 +11298,7 @@
         <f t="shared" si="35"/>
         <v>672</v>
       </c>
-      <c r="U84" s="27"/>
+      <c r="U84" s="1"/>
       <c r="V84" s="1">
         <f t="shared" si="32"/>
         <v>17.448</v>
@@ -11382,7 +11373,7 @@
       <c r="AW84" s="1"/>
       <c r="AX84" s="1"/>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>186</v>
       </c>
@@ -11437,7 +11428,7 @@
         <f t="shared" si="35"/>
         <v>252</v>
       </c>
-      <c r="U85" s="27"/>
+      <c r="U85" s="1"/>
       <c r="V85" s="1">
         <f t="shared" si="32"/>
         <v>17.142857142857142</v>
@@ -11512,7 +11503,7 @@
       <c r="AW85" s="1"/>
       <c r="AX85" s="1"/>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>187</v>
       </c>
@@ -11567,7 +11558,7 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="U86" s="27"/>
+      <c r="U86" s="1"/>
       <c r="V86" s="1">
         <f t="shared" si="32"/>
         <v>14.500000000000002</v>
@@ -11700,7 +11691,7 @@
         <f t="shared" si="35"/>
         <v>780</v>
       </c>
-      <c r="U87" s="27"/>
+      <c r="U87" s="1"/>
       <c r="V87" s="1">
         <f t="shared" si="32"/>
         <v>17.916666666666668</v>
@@ -11739,7 +11730,7 @@
       <c r="AG87" s="1">
         <v>62</v>
       </c>
-      <c r="AH87" s="1"/>
+      <c r="AH87" s="26"/>
       <c r="AI87" s="1">
         <f t="shared" si="36"/>
         <v>753.40000000000009</v>
@@ -11820,7 +11811,7 @@
       <c r="R88" s="16"/>
       <c r="S88" s="16"/>
       <c r="T88" s="16"/>
-      <c r="U88" s="26"/>
+      <c r="U88" s="14"/>
       <c r="V88" s="14">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -33146,7 +33137,24 @@
       <c r="AX497" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AO88" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AO88" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="БОНУС_Готовые чебупели сочные с мясом ТМ Горячая штучка флоу-пак 0,24 кг  ПОКОМ"/>
+        <filter val="Готовые бельмеши сочные с мясом ТМ Горячая штучка 0,3кг зам  ПОКОМ"/>
+        <filter val="Готовые круггетсы сочные ТМ Горячая штучка флоу пак 0,2кг  ПОКОМ"/>
+        <filter val="Готовые чебупели сочные с мясом 0,24 кг НОВАЯ ТМ Горячая штучка флоу-пак  ПОКОМ"/>
+        <filter val="Готовые чебупели сочные с мясом 0,48 кг НОВАЯ ТМ Горячая штучка флоу-пак МЕГАпачка  ПОКОМ"/>
+        <filter val="Готовые чебупели сочные с мясом ТМ Горячая штучка флоу-пак 0,24 кг  ПОКОМ"/>
+        <filter val="Готовые чебупели сочные с мясом ТМ Горячая штучка флоу-пак 0,48 кг XXL  Поком"/>
+        <filter val="Круггетсы сочные ТМ Горячая штучка ТС Круггетсы 0,25 кг зам  ПОКОМ"/>
+        <filter val="Круггетсы сочные ТМ Горячая штучка ТС Круггетсы флоу-пак  0,2 кг.  ПОКОМ"/>
+        <filter val="ХБИ Готовые бельмеши сочные с мясом НД1 ТМ Горячая штучка 0,3кг зам  ПОКОМ"/>
+        <filter val="Чебуреки сочные ТМ Зареченские ТС Зареченские продукты.  Поком"/>
+        <filter val="Чебуреки сочные, ВЕС, куриные жарен. зам  ПОКОМ"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
